--- a/01_전문업무_및_엔지니어링/동탄트램/동탄트램_기본설계_정합성_검토보고서.xlsx
+++ b/01_전문업무_및_엔지니어링/동탄트램/동탄트램_기본설계_정합성_검토보고서.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -493,9 +493,9 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>301 정거장</t>
+          <t>304 정거장</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -581,39 +581,33 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>정거장 캐노피 높이</t>
+          <t>승강장 연단 간격</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>-0.5999999999999996</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>기본설계상 캐노피 높이(3.2m)가 노면전차 건축한계 높이(3.8m)에 미달. 팬터그래프 상승식 급속충전 방식으로 변경됨에 따라 상향 재설계 필수</t>
+          <t>304 정거장 승강장 연단 간격</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>01. 설계보고서(건축).pdf</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/건축/01. 설계보고서(건축).pdf</t>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
         </is>
       </c>
     </row>
@@ -635,18 +629,14 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>곡선부 승강장 연단 간격</t>
+          <t>승강장 연단 간격</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>mm</t>
@@ -654,7 +644,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>건축한계 상 차량 측면으로부터 50mm 이상의 간격을 두도록 설계되었으나, R=300m 곡선에 위치하여 승차 간격이 크게 벌어짐 (발빠짐 안전사고 리스크)</t>
+          <t>304 정거장 승강장 연단 간격</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -662,9 +652,7 @@
           <t>01. 종합요약보고서.pdf</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>34</v>
-      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="4" t="inlineStr">
         <is>
           <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
@@ -674,12 +662,12 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>궤도</t>
+          <t>건축</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>201 정거장</t>
+          <t>305 정거장</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -689,51 +677,45 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>분기기 간 직선 이격거리</t>
+          <t>승강장 연단 간격</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1, 2공구 평면교차(201역) 및 차량기지 인입(209역) 특수분기기 다수 부설로 최소 직선 이격거리 기준만 간신히 충족하여 기하학적 선형 조건 크리티컬 리스크 발생</t>
+          <t>305 정거장 승강장 연단 간격</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>01. 설계보고서_궤도.pdf</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>22</v>
-      </c>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/궤도/01. 설계보고서_궤도.pdf</t>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>토목</t>
+          <t>건축</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>오산천교</t>
+          <t>305 정거장</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -743,18 +725,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>토공-교량 접속부 단차</t>
+          <t>승강장 연단 간격</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1.9</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>mm</t>
@@ -762,7 +740,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>오산천교 측면 진입 시 토공부와 교량 간 단차(처짐)가 궤도 유지관리 한계기준(3.0mm)을 초과하여 열차 탈선 리스크 유발</t>
+          <t>305 정거장 승강장 연단 간격</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -770,9 +748,7 @@
           <t>01. 종합요약보고서.pdf</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>229</v>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
@@ -782,52 +758,478 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>건축</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>일반정거장</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>정거장 캐노피 높이</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>일반정거장 정거장 캐노피 높이</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>01. 설계보고서(건축).pdf</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/건축/01. 설계보고서(건축).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>궤도</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>평면교차로</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>레일 홈(Flangeway) 간격</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>평면교차로 레일 홈(Flangeway) 간격</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>01. 설계보고서_궤도.pdf</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/궤도/01. 설계보고서_궤도.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>토목</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>오산천교</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>토공-교량 접속부 단차</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>오산천교 토공-교량 접속부 단차</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>02. 설계보고서(토목).pdf</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/02. 설계보고서(토목).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>201역</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>201역 예측소음도</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>201역</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>201역 예측소음도</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>206역</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>206역 예측소음도</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>206역</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>206역 예측소음도</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>208역</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>208역 예측소음도</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>302 정거장</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>🔴 기준 초과 (위배)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>예측소음도</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>8.799999999999997</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>dB(A)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>능동 주거시설과 23m 근접하여 운영 시 예측소음도가 소음목표기준을 크게 초과 (가설방음판넬 등 물리적 저감방안 필수)</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>302 정거장 예측소음도</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>01. 종합요약보고서.pdf</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>302 정거장</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>🔴 기준 초과 (위배)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>예측소음도</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>dB(A)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>302 정거장 예측소음도</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>01. 종합요약보고서.pdf</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>C:/Users/sskjh/antigravity/01_전문업무_및_엔지니어링/동탄트램/04_설계서/1공구/토목/01. 종합요약보고서.pdf</t>
         </is>
